--- a/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
@@ -552,10 +552,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -564,7 +564,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>9.4</v>
@@ -686,10 +686,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>31</v>
@@ -826,10 +826,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>9.4</v>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -526,7 +544,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -535,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -620,16 +638,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.67</v>
+      </c>
+      <c r="H2">
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -643,16 +664,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -663,19 +687,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -689,16 +716,19 @@
         <v>31</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="E5">
-        <v>31</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -763,7 +793,7 @@
         <v>96.67</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -800,7 +830,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -809,13 +839,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -841,7 +871,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -881,6 +911,52 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920034</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920043</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -79,22 +79,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
 </sst>
 </file>
@@ -793,7 +784,7 @@
         <v>96.67</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -810,13 +801,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H3">
         <v>8.300000000000001</v>
@@ -845,7 +836,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,7 +862,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -913,47 +904,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>20330051920059</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920043</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
@@ -784,7 +784,7 @@
         <v>96.67</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -810,7 +810,7 @@
         <v>96.88</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -836,7 +836,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -862,7 +862,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20231.xlsx
@@ -784,7 +784,7 @@
         <v>96.67</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -810,7 +810,7 @@
         <v>96.88</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -836,7 +836,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -862,7 +862,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
